--- a/src/attributions/attributions_ig_traj_201.xlsx
+++ b/src/attributions/attributions_ig_traj_201.xlsx
@@ -1568,76 +1568,76 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.3478751489252305</v>
+        <v>0.006230156101197116</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5347117314827933</v>
+        <v>0.09413696210331664</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03846060129794519</v>
+        <v>0.04308484831497747</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003249170023485482</v>
+        <v>0.04425437529062413</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3312023990736911</v>
+        <v>0.06905029098654035</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0119407342066623</v>
+        <v>0.05820464572267704</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.08126789538816524</v>
+        <v>-0.00573095002635007</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2319115838128188</v>
+        <v>-0.03343765999450256</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02229968846715871</v>
+        <v>-0.0501823581907362</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1649,25 +1649,25 @@
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.01811756018467681</v>
+        <v>0.01980792096737824</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.04315382095389502</v>
+        <v>0.06669021455682342</v>
       </c>
       <c r="AE3" t="n">
         <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0558888762692844</v>
+        <v>0.005150847932358845</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1676,46 +1676,46 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.06272069993488975</v>
+        <v>-0.08140486255682564</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.1348934363494607</v>
+        <v>0.01342779980066347</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1349081371469777</v>
+        <v>-0.16387680399726</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.01198833505137356</v>
+        <v>-0.1250009993958308</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3411621414040661</v>
+        <v>0.01229786129117517</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.36437183416922</v>
+        <v>-0.1467502265823404</v>
       </c>
       <c r="AY3" t="n">
         <v>-0</v>
@@ -1724,85 +1724,85 @@
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.1555094476034174</v>
+        <v>0.06507808967171351</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1215185890496753</v>
+        <v>0.07431752990672492</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.02871284973655372</v>
+        <v>0.2268754725033983</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.1305412044347815</v>
+        <v>0.004631069648039699</v>
       </c>
       <c r="BM3" t="n">
         <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1432047624001921</v>
+        <v>-0.01091197325957132</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.3589876543179535</v>
+        <v>-0.05981759662841292</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
         <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.02689011654727566</v>
+        <v>-0.0273425568478502</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1218826654801446</v>
+        <v>-0.01802542542777009</v>
       </c>
       <c r="BX3" t="n">
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.27479582647061</v>
+        <v>-0.05197629018354547</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
@@ -1811,19 +1811,19 @@
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.04679456193756956</v>
+        <v>-0.01551126407732097</v>
       </c>
       <c r="CE3" t="n">
         <v>-0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.1299689629682568</v>
+        <v>-0.0254723892980975</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.05089389711395803</v>
+        <v>-0.001287495611901781</v>
       </c>
       <c r="CI3" t="n">
         <v>0</v>
@@ -1835,130 +1835,130 @@
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.1731456978853478</v>
+        <v>0.02949439562724147</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.08178271362019554</v>
+        <v>0.009684386392251569</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2835191101381911</v>
+        <v>-0.05895803409472183</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
         <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.03001111823349641</v>
+        <v>-0.0073982457006095</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.1162858318855579</v>
+        <v>-0.02272035012474823</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0269213194622357</v>
+        <v>-0.01639584340228267</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1071392508230645</v>
+        <v>0.005408985741680828</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.008011643797800432</v>
+        <v>0.002272358642116867</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02923991452372426</v>
+        <v>0.1902942893664866</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.2458835054716975</v>
+        <v>0.1216136836415529</v>
       </c>
       <c r="DO3" t="n">
         <v>-0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.03688329911013297</v>
+        <v>-0.008366165163782894</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.1700991664123914</v>
+        <v>0.1252844944214938</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.07001110258327128</v>
+        <v>0.1018434656173724</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0018169823791872</v>
+        <v>-0.02090033228276881</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.1487931527748858</v>
+        <v>0.1757273976685771</v>
       </c>
       <c r="EB3" t="n">
         <v>0</v>
@@ -1967,160 +1967,160 @@
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.007975981419832589</v>
+        <v>-0.08707008343910612</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.2800634853865004</v>
+        <v>-0.01885576918493031</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.006697277721781415</v>
+        <v>0.04397417741981968</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.14237081729651</v>
+        <v>-0.01269966469115148</v>
       </c>
       <c r="EP3" t="n">
         <v>-0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.07311475410337301</v>
+        <v>0.024874642233847</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.05912778880099232</v>
+        <v>-0.05671254328403963</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.01672749802053668</v>
+        <v>-0.01879072649158638</v>
       </c>
       <c r="EY3" t="n">
         <v>-0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.1243098307548618</v>
+        <v>-0.03118348718763061</v>
       </c>
       <c r="FA3" t="n">
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01241552966454031</v>
+        <v>-0.01558225189433364</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.1172816065702273</v>
+        <v>0.0459824937848239</v>
       </c>
       <c r="FH3" t="n">
         <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0.008931537067722836</v>
+        <v>-0.07858642609747331</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1026005820474366</v>
+        <v>0.08260991103036672</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.009206128737085477</v>
+        <v>0.1027521361112596</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0.0005007494140031953</v>
+        <v>-0.0001439324416363471</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.000411127832136364</v>
+        <v>-0.003564380962092122</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.03812110888608097</v>
+        <v>0.01312910461505504</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.2158075139999436</v>
+        <v>0.03663182148422136</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
         <v>-0</v>
@@ -2129,10 +2129,10 @@
         <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,16 +2140,16 @@
         <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4120869377044308</v>
+        <v>-0.4966096287708734</v>
       </c>
       <c r="C4" t="n">
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2980519456964148</v>
+        <v>0.09946531009705252</v>
       </c>
       <c r="E4" t="n">
-        <v>0.275984372170656</v>
+        <v>0.2218049708940173</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -2167,19 +2167,19 @@
         <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1824506699301874</v>
+        <v>-0.3050100023540946</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1666111059865681</v>
+        <v>0.2123707299825532</v>
       </c>
       <c r="N4" t="n">
-        <v>0.238159781154707</v>
+        <v>0.2487436485443747</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -2191,19 +2191,19 @@
         <v>-0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.168722121471384</v>
+        <v>-0.04086445919973346</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05004899892138277</v>
+        <v>0.07779393279441342</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08120806454080912</v>
+        <v>-0.002633895920646041</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>-0</v>
@@ -2221,43 +2221,43 @@
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.1206205903413297</v>
+        <v>-0.1721923622748253</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.04722516003742221</v>
+        <v>0.1038530259150033</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.03802579889457813</v>
+        <v>-0.009214254722382473</v>
       </c>
       <c r="AG4" t="n">
         <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.1672684010195332</v>
+        <v>-0.3312212182053574</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.02961315862396113</v>
+        <v>0.09173250715515789</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1028980855486517</v>
+        <v>-0.2569146227371532</v>
       </c>
       <c r="AP4" t="n">
         <v>-0</v>
@@ -2266,61 +2266,61 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.4802007332999901</v>
+        <v>-0.4921003074509366</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1898613871468412</v>
+        <v>0.132935751931819</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.07836962770515005</v>
+        <v>0.2887606404484045</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.03023133438096697</v>
+        <v>0.04877210120197485</v>
       </c>
       <c r="BE4" t="n">
         <v>-0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.02339879976206542</v>
+        <v>0.03117270087356955</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.3549470039696818</v>
+        <v>0.2335909071027263</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>-0</v>
@@ -2329,43 +2329,43 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.00911920600749175</v>
+        <v>0.09910367539058797</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.04962031504633185</v>
+        <v>0.05824307435668132</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.0704648311385884</v>
+        <v>0.004268681202269813</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.2375004639986642</v>
+        <v>-0.3323036728403177</v>
       </c>
       <c r="BW4" t="n">
         <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.07754881491544717</v>
+        <v>0.1616088281426346</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1938422651544043</v>
+        <v>0.08781017068952111</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -2383,49 +2383,49 @@
         <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.09986702530477073</v>
+        <v>0.3226098619328225</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.02950581103074137</v>
+        <v>-0.07669599700221338</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.02377124842224986</v>
+        <v>0.005836362805610483</v>
       </c>
       <c r="CI4" t="n">
         <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>-0</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.06488571957229829</v>
+        <v>0.2102589116512381</v>
       </c>
       <c r="CO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.06456613589241621</v>
+        <v>-0.1525744716812996</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.02537455315471836</v>
+        <v>-0.08054583640161965</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
         <v>0</v>
@@ -2437,22 +2437,22 @@
         <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.08803227356162346</v>
+        <v>0.3103446871794352</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0.06027341610035197</v>
+        <v>-0.08374495308026172</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.01910588952759533</v>
+        <v>-0.0200996499985971</v>
       </c>
       <c r="DA4" t="n">
         <v>-0</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2464,22 +2464,22 @@
         <v>-0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1271601830982305</v>
+        <v>0.12811227055389</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.0004791189603886421</v>
+        <v>0.006745548777690405</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.00022475651774209</v>
+        <v>-0.0033482566466502</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>-0</v>
@@ -2491,22 +2491,22 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.1795472990511877</v>
+        <v>0.1594954246992755</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.07291969136316297</v>
+        <v>-0.09053037866590216</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.003891964142108996</v>
+        <v>0.03450932375243101</v>
       </c>
       <c r="DS4" t="n">
         <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.004813021628795083</v>
+        <v>-0.1200235665989237</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.09461997915210624</v>
+        <v>-0.1164346672895773</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.1028871297667648</v>
+        <v>-0.2284897148328254</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC4" t="n">
         <v>0</v>
@@ -2545,16 +2545,16 @@
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.1013186474106584</v>
+        <v>0.2428084062793706</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0.117079975302681</v>
+        <v>-0.02896463283222379</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.04660219521040106</v>
+        <v>-0.0138646233799247</v>
       </c>
       <c r="EK4" t="n">
         <v>0</v>
@@ -2563,25 +2563,25 @@
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.07800380128926875</v>
+        <v>0.1795166105481781</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.03607018265214927</v>
+        <v>-0.07986197049747724</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.05229241799637385</v>
+        <v>-0.07745034048742049</v>
       </c>
       <c r="ET4" t="n">
         <v>0</v>
@@ -2593,52 +2593,52 @@
         <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.07486026708867133</v>
+        <v>0.366678415937831</v>
       </c>
       <c r="EZ4" t="n">
         <v>0</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0.0533898167118099</v>
+        <v>-0.09913460142856649</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.01682477313963701</v>
+        <v>-0.009360718812140735</v>
       </c>
       <c r="FC4" t="n">
         <v>0</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.001829189904588714</v>
+        <v>0.2077910094630325</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0.1482145584436951</v>
+        <v>-0.1159209911758692</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.03571050618731016</v>
+        <v>-0.1533647116184008</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>-0</v>
@@ -2647,31 +2647,31 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP4" t="n">
         <v>0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.006016997711665722</v>
+        <v>-0.03220371214048312</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.01833644203126089</v>
+        <v>-0.1816139859531436</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.002834252159055476</v>
+        <v>0.0003237368679189984</v>
       </c>
       <c r="FU4" t="n">
         <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
         <v>-0</v>
@@ -2680,13 +2680,13 @@
         <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.02696263321801111</v>
+        <v>0.165961509458151</v>
       </c>
       <c r="GA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.08331838697230903</v>
+        <v>0.03251057907798698</v>
       </c>
       <c r="GC4" t="n">
         <v>-0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4203970612742267</v>
+        <v>-0.3902375468267102</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2381725178332416</v>
+        <v>0.1878473641023177</v>
       </c>
       <c r="E5" t="n">
-        <v>0.273264130438886</v>
+        <v>0.08867952594288413</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
@@ -2727,28 +2727,28 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3101477086637015</v>
+        <v>-0.4286505831184733</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2222121562054488</v>
+        <v>0.2669801854041424</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2696280773763496</v>
+        <v>0.1405202464332765</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2763,127 +2763,127 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1284318551118342</v>
+        <v>-0.04109162553456438</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01904545226727132</v>
+        <v>0.01533178623558822</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.07335317270094205</v>
+        <v>-0.0116301129691597</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1704161127400031</v>
+        <v>-0.03030981253780318</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.05715818951733054</v>
+        <v>0.153763654368942</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.02356619343079017</v>
+        <v>-0.2217726761944828</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.04896102394264443</v>
+        <v>-0.1440833969953473</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.04477912547546925</v>
+        <v>0.04284552320016726</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.07869489294520983</v>
+        <v>-0.2331040469144822</v>
       </c>
       <c r="AP5" t="n">
         <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.3401131025108767</v>
+        <v>-0.2425030489364495</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.06970047537053838</v>
+        <v>0.181064099648297</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.008627081229880568</v>
+        <v>0.04343781030329023</v>
       </c>
       <c r="AY5" t="n">
         <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.008829065649101577</v>
+        <v>0.03074010019572927</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.2161857308369209</v>
+        <v>0.01945866673344017</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.3428484569850302</v>
+        <v>0.09399341976463066</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
@@ -2898,16 +2898,16 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.09089568020081853</v>
+        <v>0.1097310862730086</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.02630949504052616</v>
+        <v>0.07264371408636869</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.09840232868604756</v>
+        <v>-0.01118954949787514</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
@@ -2925,25 +2925,25 @@
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.2637835255097385</v>
+        <v>-0.1862108689479959</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.005855053553077499</v>
+        <v>0.08266163169074263</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.04968715169096643</v>
+        <v>0.0009322462403479262</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
@@ -2952,16 +2952,16 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0994917647820658</v>
+        <v>0.1947108411207845</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.05981657916910861</v>
+        <v>-0.06887845048790521</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001654412517811515</v>
+        <v>-0.01049244579751373</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
@@ -2979,19 +2979,19 @@
         <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.03904433531414777</v>
+        <v>0.09077372166627176</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.08836504795522895</v>
+        <v>-0.08014811475072159</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.08395989053667714</v>
+        <v>-0.02544203126988138</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
@@ -3006,46 +3006,46 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.09909492014780513</v>
+        <v>0.2097527983783143</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.08172709137269067</v>
+        <v>-0.0736227543940539</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.01289019254973816</v>
+        <v>-0.0364095225089445</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>-0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1913335792505671</v>
+        <v>0.1500866290529764</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.09039708995659418</v>
+        <v>-0.0391471973239022</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.01612744328293991</v>
+        <v>0.0004639762198912587</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,25 +3054,25 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.05315386549332303</v>
+        <v>0.09944575259077537</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.03945751839556569</v>
+        <v>-0.07080232137162867</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.07524115673016218</v>
+        <v>0.04003092691685088</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT5" t="n">
         <v>0</v>
@@ -3087,22 +3087,22 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1090832463548563</v>
+        <v>0.04319991691164538</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.1120631691043394</v>
+        <v>0.02552862267756187</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.04292370431063442</v>
+        <v>0.003611966123300141</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,25 +3114,25 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.06261320051121112</v>
+        <v>0.2200148816607372</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.05128472242952131</v>
+        <v>-0.0515402049540205</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.1280042182459941</v>
+        <v>-0.04497360168235492</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>0</v>
@@ -3141,25 +3141,25 @@
         <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.01090740335426707</v>
+        <v>-0.1175512243664153</v>
       </c>
       <c r="EQ5" t="n">
         <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.03305469095304838</v>
+        <v>-0.01124282473495074</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02963720384945741</v>
+        <v>0.01338937614481888</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
         <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
@@ -3168,16 +3168,16 @@
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.1021779611874328</v>
+        <v>0.2340009828994381</v>
       </c>
       <c r="EZ5" t="n">
         <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.07113789239965995</v>
+        <v>-0.0846230944567089</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.01393453093228759</v>
+        <v>-0.007484793920215041</v>
       </c>
       <c r="FC5" t="n">
         <v>0</v>
@@ -3186,52 +3186,52 @@
         <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.07244239177882095</v>
+        <v>0.08649804043931243</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.1034012052979759</v>
+        <v>0.09156880849337438</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.05343306529002467</v>
+        <v>0.02003220934353154</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01786479763664515</v>
+        <v>0.1824214370626203</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.03866397923095361</v>
+        <v>0.01471591573657509</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.003043364984106816</v>
+        <v>-0.08443438783763341</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3240,37 +3240,37 @@
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.06642362777887707</v>
+        <v>0.1962122176105751</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.06278896293088311</v>
+        <v>-0.005883491887675817</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4944175880602533</v>
+        <v>0.3673263660664046</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1198894349094563</v>
+        <v>-0.03132362115763966</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4544460008606231</v>
+        <v>-0.1574310961824845</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4274607518904434</v>
+        <v>0.4485034714310024</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,25 +3314,25 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04888874850773579</v>
+        <v>-0.130178196493785</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4157528138401824</v>
+        <v>-0.1955038102499164</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04063933094066322</v>
+        <v>0.1181387580374067</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,16 +3341,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.08967454752124288</v>
+        <v>-0.1505967697670783</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.01598316809495008</v>
+        <v>-0.008656607559602366</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -3359,19 +3359,19 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.02252847513618931</v>
+        <v>-0.03162450802245122</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.008390708569729568</v>
+        <v>-0.2887825223557907</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.03544500394326719</v>
+        <v>0.003527479040623809</v>
       </c>
       <c r="AH6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.08318877872611036</v>
+        <v>0.04767021123248868</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0007077278191615895</v>
+        <v>-0.05554508401760289</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.08540701532056351</v>
+        <v>0.01816034171727798</v>
       </c>
       <c r="AQ6" t="n">
         <v>-0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4218259438604975</v>
+        <v>0.5191454181042116</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,16 +3422,16 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.06897385573744649</v>
+        <v>-0.2773316772019603</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.2205919160920708</v>
+        <v>-0.1188790333326577</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1099878069610339</v>
+        <v>-0.04339056641769333</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,52 +3449,52 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1555668212240102</v>
+        <v>-0.02496902837454742</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.2031233903851091</v>
+        <v>-0.08294885925804485</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1451342674025795</v>
+        <v>0.05824419041574769</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.002556688646453596</v>
+        <v>0.08937834520485273</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0211355153587851</v>
+        <v>-0.02766133106619291</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2207219932939731</v>
+        <v>0.280554085961145</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.06717633274302381</v>
+        <v>-0.08484454530252006</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.129854641674758</v>
+        <v>-0.1133443628907627</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.08697241061607046</v>
+        <v>-0.1241005857088528</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.005260933946613045</v>
+        <v>0.02982513345676222</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.1102993405917673</v>
+        <v>0.05788680263723674</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,49 +3548,49 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-4.43257607350541e-05</v>
+        <v>-0.1130418455220918</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.01466065102031537</v>
+        <v>0.1111120639927183</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.02412898156694127</v>
+        <v>0.09855759559282742</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.0687753690642883</v>
+        <v>-0.1207477986492186</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.001385798239291539</v>
+        <v>0.00912079538591205</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.1157981227674384</v>
+        <v>0.0813693175712514</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
@@ -3602,25 +3602,25 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.04431739291869521</v>
+        <v>-0.0540124289549061</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0469190519338525</v>
+        <v>-0.1975404969883628</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0004228659813447472</v>
+        <v>0.07982109192302066</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
         <v>0</v>
@@ -3629,19 +3629,19 @@
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.006641109162840441</v>
+        <v>-0.02073396924641933</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.03409219115504388</v>
+        <v>-0.06329309576383095</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.007839961212285225</v>
+        <v>0.08041025222081968</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3650,13 +3650,13 @@
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.05630551712360807</v>
+        <v>-0.0268568656386304</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,25 +3665,25 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01739268735557954</v>
+        <v>-0.0550253324327012</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.05349210144062201</v>
+        <v>0.04359670920676496</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
         <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.1002099334802206</v>
+        <v>-0.05013198736437276</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
@@ -3692,79 +3692,79 @@
         <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.02829821554655291</v>
+        <v>0.01336142295899115</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.1234794527568776</v>
+        <v>-0.006961048616991997</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.03354367535041377</v>
+        <v>-0.01249802592186753</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01138240262551658</v>
+        <v>-0.005899383144940205</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.07389758701291133</v>
+        <v>0.1446168996258657</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.06650577815978947</v>
+        <v>-0.1419693449424611</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.00686835868898876</v>
+        <v>-0.0004515334052908549</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.1058259541203652</v>
+        <v>0.04850484575129888</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.005797606991718213</v>
+        <v>0.2021335913128045</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,16 +3773,16 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.008269053209006944</v>
+        <v>-0.07289011355661995</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.05044232467575337</v>
+        <v>0.1309518990581542</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
@@ -3791,46 +3791,46 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.005420703803291718</v>
+        <v>0.008538417899239708</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.008628367138022312</v>
+        <v>-0.02237659527608413</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.03001674149327355</v>
+        <v>-0.04848437542451323</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.04279250744070507</v>
+        <v>-0.03346134264582198</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.05313188342164341</v>
+        <v>0.08115448268945702</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3839,7 +3839,7 @@
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1465852228526663</v>
+        <v>0.3969256418546411</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,25 +4994,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07399542798630397</v>
+        <v>-0.01718061647502239</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0709790340585276</v>
+        <v>-0.1595186744597766</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1108856173884611</v>
+        <v>0.4372282952607412</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04595669083434802</v>
+        <v>-0.1139331941005722</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06470193804116534</v>
+        <v>-0.1912269917031652</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01286623979709052</v>
+        <v>0.1044942959889899</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,40 +5048,40 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.006100835549428585</v>
+        <v>-0.09466072415932646</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009342836230473214</v>
+        <v>-0.02024099506776598</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.004928984544738137</v>
+        <v>-0.03685664010370459</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01258156439247423</v>
+        <v>-0.2552359378293638</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01050107998378377</v>
+        <v>0.045977414084051</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5093,22 +5093,22 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.009158633067053728</v>
+        <v>0.04261947115897059</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.009344143710511673</v>
+        <v>-0.03674726705645801</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.01452169277157193</v>
+        <v>0.004084694325702766</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5117,28 +5117,28 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1019198328055797</v>
+        <v>0.4298116403776999</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.02807047747016878</v>
+        <v>-0.266703631100383</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.02016552463268135</v>
+        <v>-0.1209157629426972</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03040979956368515</v>
+        <v>-0.01793593956142691</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.05200338909831748</v>
+        <v>-0.006101564241852741</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.06011200255662029</v>
+        <v>-0.06069118740482153</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03426528983123459</v>
+        <v>0.05052678002126591</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01557273011220122</v>
+        <v>0.06157330246901688</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01534036555480199</v>
+        <v>-0.01112595399125816</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.047368182566852</v>
+        <v>0.2414822798158145</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.01165554142871243</v>
+        <v>-0.05985773466473071</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.01167342535910132</v>
+        <v>-0.1240202384482711</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5225,28 +5225,28 @@
         <v>-0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.02434920044063748</v>
+        <v>-0.1137540148714066</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.006277110844750866</v>
+        <v>0.02917904079566028</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01747917093761229</v>
+        <v>0.05963678913299981</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0008711438210970087</v>
+        <v>-0.1147816444000389</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
@@ -5264,97 +5264,97 @@
         <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.004870258777359961</v>
+        <v>0.1496826747591614</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.01055356244104783</v>
+        <v>0.06868932225718427</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.01837875031968109</v>
+        <v>-0.1119537330061609</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.005788378002291633</v>
+        <v>0.01827083508161986</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01825785415799794</v>
+        <v>0.08222235311554203</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03055706956215015</v>
+        <v>-0.07805895886511502</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.04795676047248516</v>
+        <v>-0.2053762820890815</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01313787130993649</v>
+        <v>0.06667956780340208</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
         <v>-0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.004916013979101529</v>
+        <v>-0.009997958543084565</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.01919661233951572</v>
+        <v>-0.06021135600141588</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.007774198957988798</v>
+        <v>0.04169724196238191</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>-0</v>
@@ -5363,49 +5363,49 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02846097191678534</v>
+        <v>-0.005631911990851824</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01360604075316584</v>
+        <v>-0.03638945139055259</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.01789462456361692</v>
+        <v>0.01366938329681499</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.02911864151567194</v>
+        <v>-0.05787979272810461</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.008480714679931127</v>
+        <v>0.01772311591468043</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.01387669463880132</v>
+        <v>0.002135051693077886</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,22 +5414,22 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.01260822431150292</v>
+        <v>-0.03440564933223574</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.003845554478425642</v>
+        <v>-0.01208967426754717</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.01036215508293767</v>
+        <v>0.1090035198219108</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
@@ -5438,58 +5438,58 @@
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.01930000018848992</v>
+        <v>-0.1301528791426035</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.008683513147103507</v>
+        <v>0.002589470299987057</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02122334911163535</v>
+        <v>0.04926107642619053</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.01604457638516874</v>
+        <v>0.1839387303034509</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.01197799151554985</v>
+        <v>-0.07780575109705781</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.01949669269291303</v>
+        <v>0.1383156177246908</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
@@ -5498,78 +5498,78 @@
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0001186836000044023</v>
+        <v>0.002269034342212356</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.001333692896077636</v>
+        <v>-0.009107064464106952</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0182015524807463</v>
+        <v>-0.03162385840654541</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0001952809621877177</v>
+        <v>-0.040712622699525</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.00411468136418883</v>
+        <v>0.0758062636767521</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
         <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.8502837428435279</v>
+        <v>-0.2632674171497739</v>
       </c>
       <c r="B10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05655871633976203</v>
+        <v>0.209488579268205</v>
       </c>
       <c r="F10" t="n">
-        <v>1.687231382981478</v>
+        <v>0.6283093612791977</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5578,22 +5578,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4323332666266763</v>
+        <v>-0.16441393391849</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1602354216972428</v>
+        <v>0.3905909750829961</v>
       </c>
       <c r="O10" t="n">
-        <v>1.278894506970289</v>
+        <v>1.067381410106608</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5605,52 +5605,52 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1922866802710226</v>
+        <v>0.08536340758348407</v>
       </c>
       <c r="T10" t="n">
         <v>-0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>-0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5082619239813235</v>
+        <v>-0.02150163681497325</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1915377317545275</v>
+        <v>0.128464423379295</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.2231365369000803</v>
+        <v>-0.1540701535566233</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>-0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1062409241909324</v>
+        <v>0.02410445369008753</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.09126751785465746</v>
+        <v>-0.3189598640268801</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.1899579490643113</v>
+        <v>-0.08704243343982818</v>
       </c>
       <c r="AL10" t="n">
         <v>-0</v>
@@ -5671,10 +5671,10 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01888882982903044</v>
+        <v>-0.3521654900326996</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.06123801101473281</v>
+        <v>-0.02474078680267843</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -5683,52 +5683,52 @@
         <v>-0</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.6097803001632807</v>
+        <v>-0.02157083022841234</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.6201411756746733</v>
+        <v>-0.2630871735945537</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.052831566551708</v>
+        <v>0.6539432702725795</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.2060866365751479</v>
+        <v>-0.1945146997898888</v>
       </c>
       <c r="BD10" t="n">
         <v>-0</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1354846950335468</v>
+        <v>0.5691703431710214</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.1952686044250534</v>
+        <v>-0.3498127435036994</v>
       </c>
       <c r="BI10" t="n">
         <v>-0</v>
@@ -5740,10 +5740,10 @@
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.03870840396197738</v>
+        <v>0.1527822424762326</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -5752,40 +5752,40 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.06466038365058653</v>
+        <v>0.03445941759659151</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.1143795097060027</v>
+        <v>0.02567225477356964</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0.4089227988679115</v>
+        <v>-0.01203677852762843</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.3257989605731144</v>
+        <v>-0.04024737753969684</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.6145798994091752</v>
+        <v>0.3525289303833425</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
         <v>-0</v>
@@ -5794,7 +5794,7 @@
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.2339331298305126</v>
+        <v>0.07345054580648686</v>
       </c>
       <c r="CE10" t="n">
         <v>-0</v>
@@ -5806,22 +5806,22 @@
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.03677137526617377</v>
+        <v>-0.04725116843565927</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0.3353032623842591</v>
+        <v>-0.06039160539440133</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0.01918928072767162</v>
+        <v>-0.0775998314595973</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
@@ -5833,25 +5833,25 @@
         <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.5706829987925043</v>
+        <v>-0.19300799013398</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.08236883473748149</v>
+        <v>0.270372402189268</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.2203005068442297</v>
+        <v>0.08847749042046107</v>
       </c>
       <c r="CW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.03393527105203356</v>
+        <v>-0.1431402407705024</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0.3184503568692622</v>
+        <v>-0.1493073813460601</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
@@ -5872,64 +5872,64 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0.001021463966942377</v>
+        <v>0.005702698874129549</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.4784050070619013</v>
+        <v>0.1655221300707579</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.04168057656363482</v>
+        <v>-0.1487924714087882</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
         <v>-0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.1183995626040507</v>
+        <v>0.02059958295346414</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.1265712080371372</v>
+        <v>0.1345543001457302</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.09133203575488023</v>
+        <v>-0.1932710553984657</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05651170388601569</v>
+        <v>0.06870129930356661</v>
       </c>
       <c r="DX10" t="n">
         <v>-0</v>
@@ -5938,43 +5938,43 @@
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.02092785148218939</v>
+        <v>-0.1085888242326713</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.4458962471348428</v>
+        <v>-0.2807577804850698</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
         <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.150650987458159</v>
+        <v>-0.05828302996004474</v>
       </c>
       <c r="EG10" t="n">
         <v>-0</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.1534375046047704</v>
+        <v>-0.1747669799486979</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0.2033266677291174</v>
+        <v>-0.06677483701364652</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,7 +5983,7 @@
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.08454460904624655</v>
+        <v>0.02145072903661248</v>
       </c>
       <c r="EP10" t="n">
         <v>-0</v>
@@ -5995,10 +5995,10 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.3250134762032604</v>
+        <v>-0.09520561870017522</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0.06627756881633352</v>
+        <v>-0.1823384893688573</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
@@ -6007,10 +6007,10 @@
         <v>-0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.187822665324337</v>
+        <v>0.04976585726261427</v>
       </c>
       <c r="EY10" t="n">
         <v>-0</v>
@@ -6022,94 +6022,94 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.08804884683926674</v>
+        <v>-0.04071157965018422</v>
       </c>
       <c r="FC10" t="n">
-        <v>-0.2809320706643329</v>
+        <v>-0.1488192175556596</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0.09838211950112487</v>
+        <v>-0.1582405464879239</v>
       </c>
       <c r="FH10" t="n">
         <v>0</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.08654835641166246</v>
+        <v>-0.06669776593887092</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0.003487209481427227</v>
+        <v>-0.2664089717302998</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.02852771258249955</v>
+        <v>0.02585028793104953</v>
       </c>
       <c r="FQ10" t="n">
         <v>0</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.004379587628498551</v>
+        <v>0.001954674052398164</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.3123973185146371</v>
+        <v>-0.09633217170277589</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0.09610245220745987</v>
+        <v>-0.1617989115940726</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.05448303746657592</v>
+        <v>-0.09756517395285559</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
         <v>-0</v>
